--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104743_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104743_W32.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.289</v>
+        <v>2.5797</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5831</v>
+        <v>2.5746</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2941</v>
+        <v>0.0051</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1748</v>
+        <v>1.1744</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1608</v>
+        <v>1.1628</v>
       </c>
       <c r="I2" t="n">
-        <v>0.014</v>
+        <v>0.0116</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2575</v>
+        <v>2.2475</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6417</v>
+        <v>1.6375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6158</v>
+        <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0827</v>
+        <v>-1.0731</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4809</v>
+        <v>-0.4747</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6018</v>
+        <v>-0.5984</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2289</v>
+        <v>0.5144</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3256</v>
+        <v>0.3271</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.1873</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6566</v>
+        <v>1.4621</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3218</v>
+        <v>2.5981</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6652</v>
+        <v>-1.136</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8238</v>
+        <v>1.1139</v>
       </c>
       <c r="H3" t="n">
-        <v>0.955</v>
+        <v>2.0628</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8688</v>
+        <v>-0.9489</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7383</v>
+        <v>2.9623</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8122</v>
+        <v>3.3127</v>
       </c>
       <c r="L3" t="n">
-        <v>0.926</v>
+        <v>-0.3505</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08550000000000001</v>
+        <v>-1.8483</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1427</v>
+        <v>-1.2499</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0573</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0157</v>
+        <v>0.1903</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4164</v>
+        <v>-0.0863</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4322</v>
+        <v>0.2766</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4101</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4101</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4275</v>
+        <v>0.6906</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8911</v>
+        <v>1.5033</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4636</v>
+        <v>-0.8127</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1199</v>
+        <v>1.8204</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0693</v>
+        <v>0.9536</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9493</v>
+        <v>0.8667</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9765</v>
+        <v>1.7334</v>
       </c>
       <c r="K4" t="n">
-        <v>3.324</v>
+        <v>0.8101</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3475</v>
+        <v>0.9233</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8566</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2548</v>
+        <v>0.1435</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6018</v>
+        <v>-0.0565</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1359</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8518</v>
+        <v>0.0476</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8139</v>
+        <v>-0.2301</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0379</v>
+        <v>0.2777</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1594</v>
+        <v>-1.405</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8643999999999999</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.705</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3799</v>
+        <v>0.4678</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3029</v>
+        <v>1.7671</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.923</v>
+        <v>-1.2993</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0121</v>
+        <v>0.5434</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0917</v>
+        <v>0.4626</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1038</v>
+        <v>0.0808</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5862</v>
+        <v>1.3588</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3998</v>
+        <v>1.2098</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1864</v>
+        <v>0.1489</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5983</v>
+        <v>-0.8154</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3081</v>
+        <v>-0.7472</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2902</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8175</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8175</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4382</v>
+        <v>0.648</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3979</v>
+        <v>0.2505</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0403</v>
+        <v>0.3975</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8637</v>
+        <v>-1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3188</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1825</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2597</v>
+        <v>0.224</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6381</v>
+        <v>-0.925</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3784</v>
+        <v>1.149</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5422</v>
+        <v>-0.1999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4643</v>
+        <v>0.4677</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0779</v>
+        <v>-0.6676</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3648</v>
+        <v>-0.9318</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2157</v>
+        <v>0.0517</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1491</v>
+        <v>-0.9835</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8226</v>
+        <v>0.7319</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7514</v>
+        <v>0.416</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0712</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4456</v>
+        <v>-0.0313</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1138</v>
+        <v>0.0068</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3318</v>
+        <v>-0.0381</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6369</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0233</v>
+        <v>0.1855</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2765</v>
+        <v>1.8394</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2998</v>
+        <v>-1.6539</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2007</v>
+        <v>-0.0066</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4651</v>
+        <v>1.0939</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6657</v>
+        <v>-1.1005</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9295</v>
+        <v>1.5824</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0518</v>
+        <v>1.3962</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9813</v>
+        <v>0.1862</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7288</v>
+        <v>-1.589</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4132</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3156</v>
+        <v>-1.2866</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4544</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4544</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2304</v>
+        <v>0.2345</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.347</v>
+        <v>-0.0585</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1166</v>
+        <v>0.2929</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.8634</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.105</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2594</v>
+        <v>0.5558</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3644</v>
+        <v>-1.0714</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8548</v>
+        <v>-0.8603</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.45</v>
+        <v>-0.4533</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4048</v>
+        <v>-0.407</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4261</v>
+        <v>0.4144</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4441</v>
+        <v>0.4374</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.018</v>
+        <v>-0.023</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2809</v>
+        <v>-1.2747</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8941</v>
+        <v>-0.8907</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3868</v>
+        <v>-0.384</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9323</v>
+        <v>0.5236</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8333</v>
+        <v>0.1414</v>
       </c>
       <c r="U8" t="n">
-        <v>0.099</v>
+        <v>0.3823</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4553</v>
+        <v>-0.7197</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2407</v>
+        <v>-1.5237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7853</v>
+        <v>0.804</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2075</v>
+        <v>-1.2053</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6665</v>
+        <v>1.6683</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.874</v>
+        <v>-2.8736</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0752</v>
+        <v>0.0678</v>
       </c>
       <c r="K9" t="n">
-        <v>1.659</v>
+        <v>1.6547</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5838</v>
+        <v>-1.587</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2827</v>
+        <v>-1.2731</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0075</v>
+        <v>0.0135</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2902</v>
+        <v>-1.2866</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7699</v>
+        <v>-0.0395</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1799</v>
+        <v>-0.4533</v>
       </c>
       <c r="U9" t="n">
-        <v>0.41</v>
+        <v>0.4138</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.874</v>
+        <v>-1.4384</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.805</v>
+        <v>-1.4404</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6856</v>
+        <v>-2.6904</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3328</v>
+        <v>-0.3331</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3527</v>
+        <v>-2.3573</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2498</v>
+        <v>-1.259</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2877</v>
+        <v>-0.2898</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.962</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4358</v>
+        <v>-1.4314</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0451</v>
+        <v>-0.0433</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3907</v>
+        <v>-1.3881</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3244</v>
+        <v>0.1138</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5553</v>
+        <v>-0.1813</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2309</v>
+        <v>0.2951</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5975</v>
+        <v>-2.9865</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8344</v>
+        <v>-3.8979</v>
       </c>
       <c r="F11" t="n">
-        <v>1.237</v>
+        <v>0.9114</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6575</v>
+        <v>-1.6638</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3975</v>
+        <v>1.3934</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0551</v>
+        <v>-3.0572</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.202</v>
+        <v>-0.2183</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8784</v>
+        <v>1.8681</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0804</v>
+        <v>-2.0864</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4555</v>
+        <v>-1.4455</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4809</v>
+        <v>-0.4747</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3049</v>
+        <v>0.3194</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1799</v>
+        <v>-0.2164</v>
       </c>
       <c r="U11" t="n">
-        <v>0.875</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.918</v>
+        <v>-4.3751</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.954</v>
+        <v>-2.4263</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.964</v>
+        <v>-1.9488</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1083</v>
+        <v>-3.1132</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2488</v>
+        <v>-3.2531</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1405</v>
+        <v>0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9701</v>
+        <v>-1.982</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1818</v>
+        <v>-2.1901</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2117</v>
+        <v>0.2081</v>
       </c>
       <c r="M12" t="n">
+        <v>-1.1312</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1.0631</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.06809999999999999</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.1382</v>
       </c>
-      <c r="N12" t="n">
-        <v>-1.0669</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0.0712</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-0.2272</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-1.1359</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2812</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8333</v>
+        <v>0.3782</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4479</v>
+        <v>0.4509</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8637</v>
+        <v>-1.8634</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5368</v>
+        <v>-4.6364</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9206</v>
+        <v>-5.4398</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3838</v>
+        <v>0.8034</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7336</v>
+        <v>-2.7307</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1293</v>
+        <v>-0.1267</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.6044</v>
+        <v>-2.604</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7683</v>
+        <v>-1.7718</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4493</v>
+        <v>0.4482</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.2176</v>
+        <v>-2.22</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9654</v>
+        <v>-0.9588</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5786</v>
+        <v>-0.5749</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3868</v>
+        <v>-0.384</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6959</v>
+        <v>0.5982</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.2535</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4404</v>
+        <v>0.8517</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.4506</v>
+        <v>-9.061999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.034799999999999</v>
+        <v>-4.814799999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.4158</v>
+        <v>-4.247299999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.7994</v>
+        <v>-7.818099999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>5.109300000000001</v>
+        <v>5.0989</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.9086</v>
+        <v>-12.917</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3049</v>
+        <v>4.203699999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>10.4065</v>
+        <v>10.3465</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.101599999999999</v>
+        <v>-6.1432</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.1044</v>
+        <v>-12.0216</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.2974</v>
+        <v>-5.2478</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.806999999999999</v>
+        <v>-6.7737</v>
       </c>
       <c r="P14" t="n">
-        <v>2.271799999999999</v>
+        <v>2.2764</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3592</v>
+        <v>-11.3817</v>
       </c>
       <c r="R14" t="n">
-        <v>13.631</v>
+        <v>13.658</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5564</v>
+        <v>3.9481</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.733</v>
+        <v>-0.3754</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2895</v>
+        <v>4.3235</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.4794</v>
+        <v>-7.468499999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>2.752699999999999</v>
+        <v>2.7386</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.2321</v>
+        <v>-10.2071</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3562</v>
+        <v>7.16</v>
       </c>
       <c r="E15" t="n">
-        <v>5.148</v>
+        <v>5.5881</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2081</v>
+        <v>1.5718</v>
       </c>
       <c r="G15" t="n">
-        <v>3.954</v>
+        <v>3.9542</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>1.0999</v>
       </c>
       <c r="I15" t="n">
-        <v>2.854</v>
+        <v>2.8543</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9623</v>
+        <v>3.9507</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7687</v>
+        <v>1.7614</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1936</v>
+        <v>2.1893</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0083</v>
+        <v>0.0035</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6688</v>
+        <v>-0.6615</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6604</v>
+        <v>0.665</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.396</v>
+        <v>-0.5783</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0221</v>
+        <v>-0.5532</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3738</v>
+        <v>-0.0251</v>
       </c>
       <c r="V15" t="n">
-        <v>5.6157</v>
+        <v>5.6051</v>
       </c>
       <c r="W15" t="n">
-        <v>5.6157</v>
+        <v>5.6051</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8576</v>
+        <v>2.2772</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3769</v>
+        <v>1.7141</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4807</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8352</v>
+        <v>2.8356</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5977</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2349</v>
+        <v>2.2379</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0285</v>
+        <v>3.0177</v>
       </c>
       <c r="K16" t="n">
-        <v>1.239</v>
+        <v>1.2303</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7895</v>
+        <v>1.7874</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1933</v>
+        <v>-0.1821</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6387</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4454</v>
+        <v>0.4506</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9777</v>
+        <v>-0.5585</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6751</v>
+        <v>-0.3232</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3026</v>
+        <v>-0.2353</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3472</v>
+        <v>2.258</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1135</v>
+        <v>-0.0523</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2337</v>
+        <v>2.3103</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4068</v>
+        <v>1.7268</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6717</v>
+        <v>-2.2343</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0785</v>
+        <v>3.9611</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4387</v>
+        <v>1.4219</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>-1.4004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4041</v>
+        <v>2.8223</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0319</v>
+        <v>0.3049</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7063</v>
+        <v>-0.8339</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6744</v>
+        <v>1.1388</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4544</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4544</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6052</v>
+        <v>-0.6086</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4164</v>
+        <v>-0.8808</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1888</v>
+        <v>0.2722</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0913</v>
+        <v>0.2292</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0913</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3048</v>
+        <v>1.6856</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3862</v>
+        <v>1.2261</v>
       </c>
       <c r="F18" t="n">
-        <v>1.691</v>
+        <v>0.4595</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7267</v>
+        <v>0.4091</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2345</v>
+        <v>-0.6694</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9611</v>
+        <v>1.0786</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4345</v>
+        <v>0.4364</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3929</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>2.8274</v>
+        <v>0.4019</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2922</v>
+        <v>-0.0273</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8416</v>
+        <v>-0.7039</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1338</v>
+        <v>0.6766</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0447</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5575</v>
+        <v>-0.2682</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2304</v>
+        <v>-0.2998</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3271</v>
+        <v>0.0316</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2268</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5456</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0851</v>
+        <v>0.9979</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5944</v>
+        <v>-1.0281</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6795</v>
+        <v>2.026</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2149</v>
+        <v>0.3299</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1496</v>
+        <v>-0.0578</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9347</v>
+        <v>0.3877</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2533</v>
+        <v>0.6423</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3217</v>
+        <v>1.5513</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0685</v>
+        <v>-0.909</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0384</v>
+        <v>-0.3124</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1722</v>
+        <v>-1.6091</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1338</v>
+        <v>1.2967</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8175</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4078</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9827</v>
+        <v>0.2126</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7639</v>
+        <v>-0.5323</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2188</v>
+        <v>0.7449</v>
       </c>
       <c r="V19" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7963</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0335</v>
+        <v>0.3364</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1503</v>
+        <v>-1.5211</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1838</v>
+        <v>1.8575</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2725</v>
+        <v>-0.2709</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4268</v>
+        <v>-2.4267</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1543</v>
+        <v>2.1558</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3952</v>
+        <v>0.3878</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9842</v>
+        <v>-0.99</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3794</v>
+        <v>1.3778</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6677</v>
+        <v>-0.6587</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4426</v>
+        <v>-1.4367</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7749</v>
+        <v>0.778</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1466</v>
+        <v>0.4495</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1828</v>
+        <v>-0.5415</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3294</v>
+        <v>0.9911</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8165</v>
+        <v>0.0915</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3106</v>
+        <v>0.3511</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4941</v>
+        <v>-0.2596</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3498</v>
+        <v>-1.3488</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2589</v>
+        <v>-1.2571</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6914</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8183</v>
+        <v>0.8134</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5032</v>
+        <v>-1.5048</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.6574</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9092</v>
+        <v>-0.9052</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2443</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5528999999999999</v>
+        <v>-0.1743</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7449</v>
+        <v>-0.2047</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.192</v>
+        <v>0.0305</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5713</v>
+        <v>-0.2444</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3707</v>
+        <v>-1.4483</v>
       </c>
       <c r="F22" t="n">
-        <v>1.942</v>
+        <v>1.2039</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3247</v>
+        <v>0.2166</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0601</v>
+        <v>1.1488</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3848</v>
+        <v>-0.9322</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6486</v>
+        <v>0.242</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5553</v>
+        <v>2.313</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9067</v>
+        <v>-2.071</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3239</v>
+        <v>-0.0254</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6154</v>
+        <v>-1.1642</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2915</v>
+        <v>1.1388</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4544</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1359</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2077</v>
+        <v>0.6575</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8833</v>
+        <v>-0.0678</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6756</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1771</v>
+        <v>-0.7261</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4473</v>
+        <v>-0.2252</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7298</v>
+        <v>-0.5009</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3844</v>
+        <v>1.3841</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7845</v>
+        <v>-1.781</v>
       </c>
       <c r="I23" t="n">
-        <v>3.1689</v>
+        <v>3.1651</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3799</v>
+        <v>2.3719</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7025</v>
+        <v>-0.7035</v>
       </c>
       <c r="L23" t="n">
-        <v>3.0824</v>
+        <v>3.0753</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9954</v>
+        <v>-0.9877</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.082</v>
+        <v>-1.0775</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0866</v>
+        <v>0.0898</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.744</v>
+        <v>-0.2892</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5553</v>
+        <v>-0.3207</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1888</v>
+        <v>0.0316</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7444</v>
+        <v>-2.5903</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5843</v>
+        <v>-0.3572</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1602</v>
+        <v>-2.2332</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4248</v>
+        <v>-1.4188</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6905</v>
+        <v>-0.6843</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7343</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2486</v>
+        <v>0.2424</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6394</v>
+        <v>0.6378</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3908</v>
+        <v>-0.3954</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6735</v>
+        <v>-1.6612</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3299</v>
+        <v>-1.3221</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.6072</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8329</v>
+        <v>-0.5995</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0824</v>
+        <v>-0.0077</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.4507</v>
+        <v>11.2458</v>
       </c>
       <c r="E25" t="n">
-        <v>4.415799999999999</v>
+        <v>4.247199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>6.034700000000001</v>
+        <v>6.9983</v>
       </c>
       <c r="G25" t="n">
-        <v>7.799599999999999</v>
+        <v>7.817799999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.1091</v>
+        <v>-5.0989</v>
       </c>
       <c r="I25" t="n">
-        <v>12.9086</v>
+        <v>12.9168</v>
       </c>
       <c r="J25" t="n">
-        <v>12.1046</v>
+        <v>12.0217</v>
       </c>
       <c r="K25" t="n">
-        <v>5.2974</v>
+        <v>5.247800000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>6.807200000000001</v>
+        <v>6.7738</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.305</v>
+        <v>-4.2038</v>
       </c>
       <c r="N25" t="n">
-        <v>-10.4067</v>
+        <v>-10.3467</v>
       </c>
       <c r="O25" t="n">
-        <v>6.101599999999999</v>
+        <v>6.1429</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.271799999999999</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6311</v>
+        <v>-13.6581</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3594</v>
+        <v>11.3817</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.5564</v>
+        <v>-1.7647</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.2895</v>
+        <v>-4.3235</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7331</v>
+        <v>2.5591</v>
       </c>
       <c r="V25" t="n">
-        <v>7.4793</v>
+        <v>7.468599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>10.2322</v>
+        <v>10.2071</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.7528</v>
+        <v>-2.7385</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104743_W32.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104743_W32.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-10.2071</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104743_W32.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-2.7385</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
